--- a/assets/fcf/Financial Statements & Free Cash Flow - Solutions.xlsx
+++ b/assets/fcf/Financial Statements & Free Cash Flow - Solutions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox\Courses\Teaching\Financial Analytics\Course\5 - Financial Statements &amp; Free Cash Flow\1 - Async\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pdwho\Dropbox (Personal)\Courses\Teaching\Financial Analytics Spring 2025\Course\3 - Financial Statements &amp; Free Cash Flow\1 - Async\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C2049B-0820-45E0-AB9B-4052B8D8A51E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9DBB29-6825-4D94-B8A3-5AC50E05182D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10876" activeTab="1" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{6394BC74-EAE9-47A1-8528-22ED1E30B107}"/>
   </bookViews>
   <sheets>
     <sheet name="Project Description" sheetId="9" r:id="rId1"/>
@@ -252,9 +252,6 @@
     <t>You are going to start a pizza business.</t>
   </si>
   <si>
-    <t>You will raise capital will come from three sources:</t>
-  </si>
-  <si>
     <t>2. You will sell $60 of long-term bonds. You will repay $20 each year over the thee three years. Both the LoC and bond have a cost of debt of 5%.</t>
   </si>
   <si>
@@ -295,6 +292,9 @@
   </si>
   <si>
     <t>=EBIT</t>
+  </si>
+  <si>
+    <t>You will raise capital from three sources:</t>
   </si>
 </sst>
 </file>
@@ -554,6 +554,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -561,9 +564,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -903,81 +903,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CDAEB0D-3A27-486D-AC6C-E43C29FCDDD3}">
   <dimension ref="A1:A23"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -988,18 +988,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4551FB90-26B1-44C9-90FF-AB3D820DD8A7}">
   <dimension ref="A1:L57"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="30.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.06640625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="7.59765625" style="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.796875" style="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="6.06640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="53.796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.08984375" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="7.6328125" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.81640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="53.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="64" t="s">
         <v>16</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="65" t="s">
         <v>17</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="66" t="s">
         <v>30</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="67" t="s">
         <v>18</v>
       </c>
@@ -1083,11 +1083,11 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" s="71" t="s">
-        <v>84</v>
-      </c>
-      <c r="B5" s="68"/>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="69"/>
       <c r="C5" s="43">
         <f>C2-C3-C4</f>
         <v>200</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="J5" s="24"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="67" t="s">
         <v>20</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="66" t="s">
         <v>21</v>
       </c>
@@ -1141,7 +1141,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="67" t="s">
         <v>22</v>
       </c>
@@ -1162,11 +1162,11 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" s="69" t="s">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="69"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="45">
         <f>C7-C8</f>
         <v>137.19999999999999</v>
@@ -1180,11 +1180,11 @@
         <v>138.6</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" s="70" t="s">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="B10" s="70"/>
+      <c r="B10" s="71"/>
       <c r="C10" s="43">
         <f>C9*(1-$H$4)</f>
         <v>82.32</v>
@@ -1200,11 +1200,11 @@
       <c r="F10" s="27"/>
       <c r="G10" s="27"/>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" s="70" t="s">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="70"/>
+      <c r="B11" s="71"/>
       <c r="C11" s="43">
         <f>C9*$H$4</f>
         <v>54.879999999999995</v>
@@ -1221,7 +1221,7 @@
       <c r="G11" s="27"/>
       <c r="I11" s="29"/>
     </row>
-    <row r="14" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="62" t="s">
         <v>59</v>
       </c>
@@ -1236,7 +1236,7 @@
       <c r="J14" s="62"/>
       <c r="K14" s="62"/>
     </row>
-    <row r="15" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
         <v>11</v>
       </c>
@@ -1268,7 +1268,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>0</v>
       </c>
@@ -1310,7 +1310,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>1</v>
       </c>
@@ -1348,7 +1348,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="11" t="s">
         <v>2</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>3</v>
       </c>
@@ -1427,13 +1427,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
       <c r="J20" s="18"/>
       <c r="K20" s="18"/>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G21" s="11" t="s">
         <v>9</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="G22" s="3" t="s">
         <v>10</v>
       </c>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>54</v>
       </c>
@@ -1513,7 +1513,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="11" t="s">
         <v>55</v>
       </c>
@@ -1551,7 +1551,7 @@
         <v>248.22</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A26" s="12" t="s">
         <v>4</v>
       </c>
@@ -1594,13 +1594,13 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="H28" s="18"/>
       <c r="I28" s="18"/>
       <c r="J28" s="18"/>
       <c r="K28" s="18"/>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="8" t="s">
         <v>5</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="62" t="s">
         <v>58</v>
       </c>
@@ -1655,7 +1655,7 @@
       <c r="J32" s="62"/>
       <c r="K32" s="62"/>
     </row>
-    <row r="33" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="2" t="s">
         <v>11</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>0</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>36</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="6" t="s">
         <v>4</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="8" t="s">
         <v>5</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -1867,7 +1867,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
@@ -1887,7 +1887,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="1" t="s">
         <v>42</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="1" t="s">
         <v>39</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="1" t="s">
         <v>40</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>-80</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A45" s="26" t="s">
         <v>41</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="8" t="s">
         <v>38</v>
       </c>
@@ -1991,7 +1991,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="28" t="s">
         <v>45</v>
       </c>
@@ -2007,7 +2007,7 @@
       <c r="E48" s="63"/>
       <c r="F48" s="63"/>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="28"/>
       <c r="B49" s="36"/>
       <c r="C49" s="61"/>
@@ -2015,13 +2015,13 @@
       <c r="E49" s="61"/>
       <c r="F49" s="61"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="H56" s="18"/>
       <c r="I56" s="18"/>
       <c r="J56" s="18"/>
       <c r="K56" s="18"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="G57" s="8"/>
       <c r="H57" s="21"/>
       <c r="I57" s="21"/>
@@ -2056,13 +2056,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B808E4-6AC2-46C9-910E-C3B9121AAE5D}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.53125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" style="40" customWidth="1"/>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" style="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>60</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2121,7 +2121,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="26" t="s">
         <v>6</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>36</v>
       </c>
@@ -2163,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>61</v>
       </c>
@@ -2191,13 +2191,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE4C7060-AB49-423F-8EF8-B072503A9C7A}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -2234,7 +2234,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="12" t="s">
         <v>57</v>
       </c>
@@ -2283,13 +2283,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F38DC4EB-101F-40DF-969D-2263D791CE3A}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="8.59765625" customWidth="1"/>
+    <col min="1" max="1" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -2306,7 +2306,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="30" t="s">
         <v>47</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="31" t="s">
         <v>49</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2382,7 +2382,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="15" t="s">
         <v>48</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>83.16</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
         <v>46</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>248.22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="8" t="s">
         <v>15</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>448.22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
@@ -2460,7 +2460,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>51</v>
       </c>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="14.65" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="34" t="s">
         <v>13</v>
       </c>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="28" t="s">
         <v>9</v>
       </c>
